--- a/data/trans_dic/P16A13-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,14</t>
+          <t>0,59; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,6</t>
+          <t>0,84; 3,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,05</t>
+          <t>0,23; 2,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,06</t>
+          <t>0,25; 2,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,56; 1,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,12</t>
+          <t>0,61; 2,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,07</t>
+          <t>0,37; 2,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,26</t>
+          <t>0,05; 4,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,79</t>
+          <t>0,9; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,55</t>
+          <t>1,23; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,19</t>
+          <t>0,84; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,84</t>
+          <t>0,35; 3,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,26</t>
+          <t>0,47; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,55</t>
+          <t>1,11; 3,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,97</t>
+          <t>0,82; 2,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,55</t>
+          <t>0,38; 2,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,14</t>
+          <t>0,86; 2,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,19</t>
+          <t>1,46; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,57</t>
+          <t>1,04; 2,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,1</t>
+          <t>0,58; 2,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,84</t>
+          <t>1,33; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,38</t>
+          <t>1,54; 4,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,23</t>
+          <t>1,04; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,47</t>
+          <t>0,92; 3,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,96</t>
+          <t>1,03; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,81</t>
+          <t>1,99; 4,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,03</t>
+          <t>0,73; 2,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,18</t>
+          <t>1,87; 4,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,41; 2,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,95</t>
+          <t>2,1; 3,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,67</t>
+          <t>1,1; 2,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,29</t>
+          <t>1,71; 3,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,42</t>
+          <t>1,38; 4,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,65</t>
+          <t>3,41; 7,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,77</t>
+          <t>1,21; 3,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,67</t>
+          <t>1,69; 6,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,08</t>
+          <t>2,54; 5,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,8</t>
+          <t>4,33; 8,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,49</t>
+          <t>0,95; 3,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,03</t>
+          <t>3,33; 5,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,59</t>
+          <t>2,31; 4,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,18</t>
+          <t>4,4; 7,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,95</t>
+          <t>1,26; 2,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,7</t>
+          <t>2,76; 5,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,0</t>
+          <t>2,23; 6,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,63</t>
+          <t>1,95; 5,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,04</t>
+          <t>3,39; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,75</t>
+          <t>6,37; 10,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,59</t>
+          <t>3,75; 8,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,28</t>
+          <t>5,17; 10,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 11,0</t>
+          <t>5,49; 10,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,24</t>
+          <t>8,53; 12,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,72</t>
+          <t>3,48; 6,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,16</t>
+          <t>4,02; 7,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,59</t>
+          <t>5,11; 8,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 10,9</t>
+          <t>7,84; 10,66</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,08</t>
+          <t>2,35; 7,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,24</t>
+          <t>4,41; 11,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,07</t>
+          <t>3,28; 8,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,08</t>
+          <t>9,66; 14,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,42</t>
+          <t>5,07; 10,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,92; 14,53</t>
+          <t>7,98; 14,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,11</t>
+          <t>4,33; 9,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 16,05</t>
+          <t>4,06; 16,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,91</t>
+          <t>4,3; 8,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,88</t>
+          <t>7,28; 11,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,58</t>
+          <t>4,27; 7,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,34</t>
+          <t>5,78; 14,52</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,17</t>
+          <t>4,37; 11,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,03; 18,31</t>
+          <t>8,94; 18,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,8</t>
+          <t>4,63; 10,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,57; 23,86</t>
+          <t>16,44; 23,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,32</t>
+          <t>4,3; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 14,89</t>
+          <t>7,75; 14,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 14,54</t>
+          <t>7,51; 15,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,16; 30,1</t>
+          <t>24,29; 30,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,7</t>
+          <t>5,09; 9,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,75</t>
+          <t>9,21; 14,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 12,29</t>
+          <t>7,31; 12,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,05; 26,69</t>
+          <t>21,75; 26,35</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,32</t>
+          <t>2,15; 3,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,87</t>
+          <t>3,43; 4,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,61</t>
+          <t>2,36; 3,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,97</t>
+          <t>4,55; 6,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,21</t>
+          <t>3,01; 4,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,23</t>
+          <t>4,59; 6,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,83</t>
+          <t>3,44; 4,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,69</t>
+          <t>6,44; 8,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,53</t>
+          <t>2,72; 3,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,31</t>
+          <t>4,26; 5,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,98</t>
+          <t>3,05; 4,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,63</t>
+          <t>6,02; 7,58</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8834</t>
+          <t>0; 8434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2255; 14222</t>
+          <t>2682; 14544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 10473</t>
+          <t>0; 10989</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 24404</t>
+          <t>0; 32644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4596; 16813</t>
+          <t>3943; 16520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>966; 8794</t>
+          <t>980; 9831</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1707; 12120</t>
+          <t>1001; 11381</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9014</t>
+          <t>0; 10144</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5570; 20310</t>
+          <t>5415; 19039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4749; 18685</t>
+          <t>5351; 19278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2998; 16842</t>
+          <t>3026; 17005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>352; 44624</t>
+          <t>330; 31428</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6271; 20543</t>
+          <t>6601; 20693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8512; 24379</t>
+          <t>8464; 25193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4917; 18809</t>
+          <t>4959; 18827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1567; 12036</t>
+          <t>1466; 13090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2934; 14165</t>
+          <t>2958; 15015</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6274; 21656</t>
+          <t>6750; 22468</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4554; 16723</t>
+          <t>4605; 16782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2119; 13021</t>
+          <t>1944; 13556</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11985; 29172</t>
+          <t>11684; 30051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18575; 41266</t>
+          <t>18900; 42145</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11108; 29644</t>
+          <t>11963; 30177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5217; 19628</t>
+          <t>5447; 19447</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8572; 24496</t>
+          <t>8469; 25094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10534; 29805</t>
+          <t>10442; 28175</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6382; 21627</t>
+          <t>6947; 22602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4380; 18625</t>
+          <t>4949; 18363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7004; 20448</t>
+          <t>7089; 21836</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14229; 33942</t>
+          <t>14036; 34100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5306; 20025</t>
+          <t>4861; 19393</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10504; 22681</t>
+          <t>10165; 23277</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18134; 40071</t>
+          <t>18659; 38331</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28510; 54816</t>
+          <t>29037; 54773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14760; 35511</t>
+          <t>14664; 34281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17862; 35472</t>
+          <t>18457; 35754</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7632; 22922</t>
+          <t>7181; 22684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21415; 47026</t>
+          <t>20979; 45144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8058; 24364</t>
+          <t>7794; 24935</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15868; 59233</t>
+          <t>15020; 60157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13553; 31344</t>
+          <t>13120; 30647</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26929; 54066</t>
+          <t>26612; 52174</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6215; 22666</t>
+          <t>6134; 20586</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23749; 42963</t>
+          <t>23754; 41104</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24588; 47492</t>
+          <t>23924; 47646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52083; 88257</t>
+          <t>54086; 88909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17374; 38204</t>
+          <t>16331; 37903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39559; 91209</t>
+          <t>44153; 93610</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8846; 23207</t>
+          <t>8630; 23283</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8209; 24130</t>
+          <t>8351; 23072</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15879; 38444</t>
+          <t>16190; 36083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35339; 60236</t>
+          <t>35711; 59500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15393; 34700</t>
+          <t>15152; 34417</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22486; 46035</t>
+          <t>23148; 46814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29065; 54665</t>
+          <t>27300; 52782</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46543; 66684</t>
+          <t>46453; 66613</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28856; 53136</t>
+          <t>27548; 51762</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35424; 62745</t>
+          <t>35191; 63008</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49189; 83769</t>
+          <t>49818; 81497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>88291; 120497</t>
+          <t>86630; 117779</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6201; 20727</t>
+          <t>6886; 21628</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13283; 34233</t>
+          <t>13423; 35647</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10087; 26973</t>
+          <t>10978; 26912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36445; 55508</t>
+          <t>35582; 55160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17750; 35740</t>
+          <t>17386; 36530</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28027; 51427</t>
+          <t>28247; 51671</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15864; 34422</t>
+          <t>16346; 36864</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23949; 97618</t>
+          <t>24719; 97571</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27943; 50285</t>
+          <t>27334; 51907</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47311; 78212</t>
+          <t>47944; 78176</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29330; 53994</t>
+          <t>30402; 54982</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57027; 140068</t>
+          <t>56425; 141785</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9781; 25546</t>
+          <t>9169; 24152</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22482; 45593</t>
+          <t>22253; 45728</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11806; 27768</t>
+          <t>11890; 26460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46858; 67454</t>
+          <t>46474; 66664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14778; 34459</t>
+          <t>14356; 33876</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30989; 57591</t>
+          <t>29964; 54140</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30135; 58203</t>
+          <t>30052; 60016</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>102606; 127847</t>
+          <t>103185; 128770</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27884; 52739</t>
+          <t>27674; 52280</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57299; 93809</t>
+          <t>58532; 93248</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45679; 80792</t>
+          <t>48013; 80768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>156012; 188833</t>
+          <t>153844; 186435</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>70617; 108614</t>
+          <t>70576; 106821</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>114170; 166447</t>
+          <t>117282; 167490</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>81052; 122688</t>
+          <t>80122; 121868</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>164059; 241010</t>
+          <t>157256; 239591</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>101921; 142388</t>
+          <t>101559; 142806</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>163853; 220822</t>
+          <t>162886; 219087</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>119777; 171144</t>
+          <t>121848; 171702</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>231207; 317937</t>
+          <t>235759; 319722</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>178837; 234861</t>
+          <t>181139; 237608</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>295469; 369878</t>
+          <t>296390; 368209</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>213981; 276229</t>
+          <t>211384; 277284</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>430868; 543050</t>
+          <t>428459; 539202</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A13-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A13-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,21</t>
+          <t>0,49; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,53</t>
+          <t>0,97; 3,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,29</t>
+          <t>0,23; 2,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,88</t>
+          <t>0,25; 2,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,98</t>
+          <t>0,56; 2,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,18</t>
+          <t>0,53; 2,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,09</t>
+          <t>0,37; 2,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,41</t>
+          <t>0,21; 2,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,81</t>
+          <t>0,86; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,67</t>
+          <t>1,24; 3,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,19</t>
+          <t>0,84; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,09</t>
+          <t>0,52; 3,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,4</t>
+          <t>0,48; 2,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,69</t>
+          <t>0,99; 3,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,98</t>
+          <t>0,81; 2,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,65</t>
+          <t>0,54; 2,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,21</t>
+          <t>0,85; 2,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,25</t>
+          <t>1,33; 3,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,61</t>
+          <t>1,0; 2,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,08</t>
+          <t>0,78; 2,52</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,94</t>
+          <t>1,36; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,14</t>
+          <t>1,54; 4,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,38</t>
+          <t>1,02; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,42</t>
+          <t>0,72; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,17</t>
+          <t>1,01; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,83</t>
+          <t>1,95; 4,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,93</t>
+          <t>0,82; 2,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,29</t>
+          <t>1,99; 4,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,89</t>
+          <t>1,39; 2,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,95</t>
+          <t>2,02; 4,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,58</t>
+          <t>1,09; 2,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,31</t>
+          <t>1,63; 3,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,37</t>
+          <t>1,39; 4,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,34</t>
+          <t>3,52; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,86</t>
+          <t>1,24; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,78</t>
+          <t>4,62; 8,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,94</t>
+          <t>2,58; 6,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,5</t>
+          <t>4,32; 8,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,17</t>
+          <t>0,94; 3,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,77</t>
+          <t>3,61; 6,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,6</t>
+          <t>2,28; 4,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,24</t>
+          <t>4,39; 7,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,93</t>
+          <t>1,34; 3,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,85</t>
+          <t>4,43; 6,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,02</t>
+          <t>2,33; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,39</t>
+          <t>1,95; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,55</t>
+          <t>3,24; 7,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,62</t>
+          <t>6,08; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,52</t>
+          <t>3,78; 8,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,45</t>
+          <t>5,16; 10,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,62</t>
+          <t>5,59; 10,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,23</t>
+          <t>8,58; 12,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,55</t>
+          <t>3,46; 6,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,19</t>
+          <t>3,95; 7,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,36</t>
+          <t>5,07; 8,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,66</t>
+          <t>7,64; 10,37</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,39</t>
+          <t>2,39; 7,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 11,71</t>
+          <t>4,51; 11,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,05</t>
+          <t>2,95; 7,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,98</t>
+          <t>9,26; 14,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,65</t>
+          <t>5,02; 10,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,98; 14,6</t>
+          <t>8,04; 14,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,76</t>
+          <t>4,07; 9,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,04</t>
+          <t>12,82; 17,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,17</t>
+          <t>4,36; 7,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,87</t>
+          <t>7,05; 11,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,72</t>
+          <t>4,15; 7,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 14,52</t>
+          <t>11,59; 15,23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,51</t>
+          <t>4,69; 11,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,36</t>
+          <t>8,56; 17,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,3</t>
+          <t>4,62; 10,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 23,58</t>
+          <t>15,91; 22,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,15</t>
+          <t>4,28; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,0</t>
+          <t>7,75; 14,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 15,0</t>
+          <t>7,87; 15,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,29; 30,32</t>
+          <t>23,79; 29,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,61</t>
+          <t>5,21; 9,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,67</t>
+          <t>9,16; 14,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,31; 12,29</t>
+          <t>6,93; 11,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,75; 26,35</t>
+          <t>21,17; 25,76</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,26</t>
+          <t>2,14; 3,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,9</t>
+          <t>3,4; 4,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,59</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,93</t>
+          <t>5,49; 7,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,23</t>
+          <t>3,02; 4,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 6,18</t>
+          <t>4,67; 6,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,84</t>
+          <t>3,36; 4,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,74</t>
+          <t>7,65; 9,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,57</t>
+          <t>2,74; 3,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,29</t>
+          <t>4,23; 5,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,0</t>
+          <t>3,07; 3,99</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,58</t>
+          <t>6,79; 7,9</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>6503</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 8434</t>
+          <t>0; 8313</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2682; 14544</t>
+          <t>2214; 14870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 10989</t>
+          <t>0; 10742</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 32644</t>
+          <t>0; 16618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3943; 16520</t>
+          <t>4538; 15869</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>980; 9831</t>
+          <t>973; 9667</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1001; 11381</t>
+          <t>1002; 10991</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 10144</t>
+          <t>0; 9292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5415; 19039</t>
+          <t>5397; 19581</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5351; 19278</t>
+          <t>4697; 18771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3026; 17005</t>
+          <t>2995; 17279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>330; 31428</t>
+          <t>1644; 18237</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>14699</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6601; 20693</t>
+          <t>6348; 20169</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8464; 25193</t>
+          <t>8522; 25801</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4959; 18827</t>
+          <t>4983; 18569</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1466; 13090</t>
+          <t>2490; 15723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2958; 15015</t>
+          <t>3032; 14420</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6750; 22468</t>
+          <t>6051; 21889</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4605; 16782</t>
+          <t>4549; 16513</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1944; 13556</t>
+          <t>2720; 14420</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11684; 30051</t>
+          <t>11609; 29101</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18900; 42145</t>
+          <t>17218; 39407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11963; 30177</t>
+          <t>11565; 29452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5447; 19447</t>
+          <t>7597; 24633</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>28423</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8469; 25094</t>
+          <t>8656; 24520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10442; 28175</t>
+          <t>10502; 29561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6947; 22602</t>
+          <t>6857; 21440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4949; 18363</t>
+          <t>4445; 17363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7089; 21836</t>
+          <t>6989; 22245</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14036; 34100</t>
+          <t>13763; 34241</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4861; 19393</t>
+          <t>5424; 18925</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10165; 23277</t>
+          <t>12407; 27162</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18659; 38331</t>
+          <t>18485; 39342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29037; 54773</t>
+          <t>27993; 55859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14664; 34281</t>
+          <t>14561; 34629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18457; 35754</t>
+          <t>20295; 38599</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>78561</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7181; 22684</t>
+          <t>7207; 23277</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20979; 45144</t>
+          <t>21624; 44684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7794; 24935</t>
+          <t>7989; 24090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15020; 60157</t>
+          <t>32352; 58763</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13120; 30647</t>
+          <t>13312; 31117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26612; 52174</t>
+          <t>26501; 52123</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6134; 20586</t>
+          <t>6099; 20589</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23754; 41104</t>
+          <t>26612; 44418</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23924; 47646</t>
+          <t>23555; 48165</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54086; 88909</t>
+          <t>53907; 89909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16331; 37903</t>
+          <t>17360; 39482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44153; 93610</t>
+          <t>63631; 95735</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>102350</t>
+          <t>109541</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8630; 23283</t>
+          <t>8997; 23694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8351; 23072</t>
+          <t>8366; 24460</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16190; 36083</t>
+          <t>15486; 38084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35711; 59500</t>
+          <t>37011; 60815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15152; 34417</t>
+          <t>15282; 35164</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23148; 46814</t>
+          <t>23096; 46396</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27300; 52782</t>
+          <t>27767; 52929</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46453; 66613</t>
+          <t>52102; 72873</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27548; 51762</t>
+          <t>27375; 51189</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35191; 63008</t>
+          <t>34591; 63031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49818; 81497</t>
+          <t>49464; 82075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86630; 117779</t>
+          <t>92862; 126044</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>66099</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>106322</t>
+          <t>113286</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6886; 21628</t>
+          <t>6995; 21507</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13423; 35647</t>
+          <t>13741; 35807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10978; 26912</t>
+          <t>9865; 25466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35582; 55160</t>
+          <t>37698; 58514</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17386; 36530</t>
+          <t>17204; 35855</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28247; 51671</t>
+          <t>28466; 50862</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16346; 36864</t>
+          <t>15381; 34808</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24719; 97571</t>
+          <t>56316; 78000</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27334; 51907</t>
+          <t>27734; 50687</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47944; 78176</t>
+          <t>46403; 78031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30402; 54982</t>
+          <t>29586; 55656</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>56425; 141785</t>
+          <t>98118; 128844</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>60279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>114184</t>
+          <t>121802</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>170701</t>
+          <t>182080</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9169; 24152</t>
+          <t>9845; 23904</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22253; 45728</t>
+          <t>21327; 43461</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11890; 26460</t>
+          <t>11874; 27027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46474; 66664</t>
+          <t>49347; 71180</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14356; 33876</t>
+          <t>14287; 33898</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29964; 54140</t>
+          <t>29971; 54899</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30052; 60016</t>
+          <t>31486; 60302</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>103185; 128770</t>
+          <t>110264; 136160</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27674; 52280</t>
+          <t>28357; 52245</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58532; 93248</t>
+          <t>58236; 91966</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48013; 80768</t>
+          <t>45519; 78459</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>153844; 186435</t>
+          <t>163810; 199306</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>70576; 106821</t>
+          <t>70173; 105971</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>117282; 167490</t>
+          <t>116213; 165627</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>80122; 121868</t>
+          <t>82159; 123631</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>157256; 239591</t>
+          <t>193771; 249185</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>101559; 142806</t>
+          <t>102113; 142944</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>162886; 219087</t>
+          <t>165743; 220736</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>121848; 171702</t>
+          <t>119203; 171138</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>235759; 319722</t>
+          <t>285399; 338445</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>181139; 237608</t>
+          <t>182237; 239500</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>296390; 368209</t>
+          <t>294840; 368516</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211384; 277284</t>
+          <t>213192; 277135</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>428459; 539202</t>
+          <t>493532; 573701</t>
         </is>
       </c>
     </row>
